--- a/Input/Takaful_Nas/rateSheet.xlsx
+++ b/Input/Takaful_Nas/rateSheet.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="26">
   <si>
     <t xml:space="preserve">planName</t>
   </si>
@@ -29,6 +29,9 @@
   </si>
   <si>
     <t xml:space="preserve">coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gender</t>
   </si>
   <si>
     <t xml:space="preserve">ageStart</t>
@@ -40,13 +43,13 @@
     <t xml:space="preserve">rates</t>
   </si>
   <si>
-    <t xml:space="preserve">gender</t>
-  </si>
-  <si>
     <t xml:space="preserve">copay</t>
   </si>
   <si>
     <t xml:space="preserve">frequency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">currency</t>
   </si>
   <si>
     <t xml:space="preserve">Zumurrod</t>
@@ -65,6 +68,9 @@
   </si>
   <si>
     <t xml:space="preserve">Annually</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USD</t>
   </si>
   <si>
     <t xml:space="preserve">female</t>
@@ -203,7 +209,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I121"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="11.52"/>
@@ -237,3485 +243,3848 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="0" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="F2" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="n">
         <v>9085</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J2" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="G3" s="1" t="n">
         <v>6705</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="F4" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="G4" s="1" t="n">
         <v>7142</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="F5" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="G5" s="1" t="n">
         <v>10826</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J5" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="F6" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="G6" s="1" t="n">
         <v>11452</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J6" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="F7" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="G7" s="1" t="n">
         <v>8675</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J7" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="F8" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="G8" s="1" t="n">
         <v>9282</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J8" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="F9" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="G9" s="1" t="n">
         <v>11542</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J9" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="F10" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="G10" s="1" t="n">
         <v>14427</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J10" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="F11" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="G11" s="1" t="n">
         <v>18216</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J11" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="F12" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F12" s="1" t="n">
+      <c r="G12" s="1" t="n">
         <v>23940</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J12" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="F13" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="F13" s="1" t="n">
+      <c r="G13" s="1" t="n">
         <v>30530</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J13" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="F14" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="G14" s="1" t="n">
         <v>9994</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J14" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="E15" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="F15" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F15" s="1" t="n">
+      <c r="G15" s="1" t="n">
         <v>7502</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J15" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="F16" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F16" s="1" t="n">
+      <c r="G16" s="1" t="n">
         <v>14293</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J16" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="F17" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F17" s="1" t="n">
+      <c r="G17" s="1" t="n">
         <v>21666</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J17" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="F18" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="F18" s="1" t="n">
+      <c r="G18" s="1" t="n">
         <v>24276</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J18" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="E19" s="1" t="n">
+      <c r="F19" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F19" s="1" t="n">
+      <c r="G19" s="1" t="n">
         <v>12253</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J19" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="F20" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="F20" s="1" t="n">
+      <c r="G20" s="1" t="n">
         <v>13617</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J20" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="E21" s="1" t="n">
+      <c r="F21" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F21" s="1" t="n">
+      <c r="G21" s="1" t="n">
         <v>15005</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J21" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="E22" s="1" t="n">
+      <c r="F22" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="F22" s="1" t="n">
+      <c r="G22" s="1" t="n">
         <v>17313</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J22" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="E23" s="1" t="n">
+      <c r="F23" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F23" s="1" t="n">
+      <c r="G23" s="1" t="n">
         <v>21859</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J23" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="E24" s="1" t="n">
+      <c r="F24" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F24" s="1" t="n">
+      <c r="G24" s="1" t="n">
         <v>26333</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J24" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="E25" s="1" t="n">
+      <c r="F25" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="F25" s="1" t="n">
+      <c r="G25" s="1" t="n">
         <v>30530</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J25" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="F26" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="G26" s="1" t="n">
         <v>7966</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J26" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E27" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="F27" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F27" s="1" t="n">
+      <c r="G27" s="1" t="n">
         <v>5405</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J27" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="E28" s="1" t="n">
+      <c r="F28" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F28" s="1" t="n">
+      <c r="G28" s="1" t="n">
         <v>5758</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J28" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="E29" s="1" t="n">
+      <c r="F29" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F29" s="1" t="n">
+      <c r="G29" s="1" t="n">
         <v>6109</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J29" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="E30" s="1" t="n">
+      <c r="F30" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="F30" s="1" t="n">
+      <c r="G30" s="1" t="n">
         <v>9232</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J30" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="E31" s="1" t="n">
+      <c r="F31" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F31" s="1" t="n">
+      <c r="G31" s="1" t="n">
         <v>7147</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H31" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J31" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="E32" s="1" t="n">
+      <c r="F32" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="F32" s="1" t="n">
+      <c r="G32" s="1" t="n">
         <v>7647</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H32" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J32" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="E33" s="1" t="n">
+      <c r="F33" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F33" s="1" t="n">
+      <c r="G33" s="1" t="n">
         <v>9880</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H33" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J33" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D34" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="E34" s="1" t="n">
+      <c r="F34" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="F34" s="1" t="n">
+      <c r="G34" s="1" t="n">
         <v>12350</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H34" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J34" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D35" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="E35" s="1" t="n">
+      <c r="F35" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F35" s="1" t="n">
+      <c r="G35" s="1" t="n">
         <v>15533</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H35" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J35" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D36" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="E36" s="1" t="n">
+      <c r="F36" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F36" s="1" t="n">
+      <c r="G36" s="1" t="n">
         <v>20365</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H36" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J36" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D37" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="E37" s="1" t="n">
+      <c r="F37" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="F37" s="1" t="n">
+      <c r="G37" s="1" t="n">
         <v>25936</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H37" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J37" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D38" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E38" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="F38" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="G38" s="1" t="n">
         <v>8301</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H38" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J38" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D39" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="E39" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="F39" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F39" s="1" t="n">
+      <c r="G39" s="1" t="n">
         <v>5934</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H39" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J39" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D40" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="E40" s="1" t="n">
+      <c r="F40" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F40" s="1" t="n">
+      <c r="G40" s="1" t="n">
         <v>13988</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H40" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J40" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D41" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="E41" s="1" t="n">
+      <c r="F41" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F41" s="1" t="n">
+      <c r="G41" s="1" t="n">
         <v>16509</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H41" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J41" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E42" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="E42" s="1" t="n">
+      <c r="F42" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="F42" s="1" t="n">
+      <c r="G42" s="1" t="n">
         <v>9723</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H42" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J42" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D43" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="E43" s="1" t="n">
+      <c r="F43" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F43" s="1" t="n">
+      <c r="G43" s="1" t="n">
         <v>9673</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H43" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J43" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D44" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="E44" s="1" t="n">
+      <c r="F44" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="F44" s="1" t="n">
+      <c r="G44" s="1" t="n">
         <v>11037</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H44" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J44" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D45" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="E45" s="1" t="n">
+      <c r="F45" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F45" s="1" t="n">
+      <c r="G45" s="1" t="n">
         <v>12844</v>
       </c>
-      <c r="G45" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H45" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J45" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D46" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="E46" s="1" t="n">
+      <c r="F46" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="F46" s="1" t="n">
+      <c r="G46" s="1" t="n">
         <v>14820</v>
       </c>
-      <c r="G46" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H46" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J46" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D47" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="E47" s="1" t="n">
+      <c r="F47" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F47" s="1" t="n">
+      <c r="G47" s="1" t="n">
         <v>18640</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H47" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J47" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D48" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="E48" s="1" t="n">
+      <c r="F48" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F48" s="1" t="n">
+      <c r="G48" s="1" t="n">
         <v>22401</v>
       </c>
-      <c r="G48" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H48" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J48" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D49" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E49" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="E49" s="1" t="n">
+      <c r="F49" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="F49" s="1" t="n">
+      <c r="G49" s="1" t="n">
         <v>25936</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H49" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J49" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D50" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E50" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="F50" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="G50" s="1" t="n">
         <v>5548</v>
       </c>
-      <c r="G50" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H50" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J50" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D51" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E51" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="F51" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F51" s="1" t="n">
+      <c r="G51" s="1" t="n">
         <v>3749</v>
       </c>
-      <c r="G51" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H51" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J51" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D52" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="E52" s="1" t="n">
+      <c r="F52" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F52" s="1" t="n">
+      <c r="G52" s="1" t="n">
         <v>3993</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H52" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J52" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D53" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="E53" s="1" t="n">
+      <c r="F53" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F53" s="1" t="n">
+      <c r="G53" s="1" t="n">
         <v>4238</v>
       </c>
-      <c r="G53" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H53" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J53" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D54" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="E54" s="1" t="n">
+      <c r="F54" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="F54" s="1" t="n">
+      <c r="G54" s="1" t="n">
         <v>4482</v>
       </c>
-      <c r="G54" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H54" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J54" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D55" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="E55" s="1" t="n">
+      <c r="F55" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F55" s="1" t="n">
+      <c r="G55" s="1" t="n">
         <v>4926</v>
       </c>
-      <c r="G55" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H55" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J55" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D56" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="E56" s="1" t="n">
+      <c r="F56" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="F56" s="1" t="n">
+      <c r="G56" s="1" t="n">
         <v>5270</v>
       </c>
-      <c r="G56" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H56" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J56" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D57" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="E57" s="1" t="n">
+      <c r="F57" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F57" s="1" t="n">
+      <c r="G57" s="1" t="n">
         <v>6747</v>
       </c>
-      <c r="G57" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H57" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J57" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D58" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="E58" s="1" t="n">
+      <c r="F58" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="F58" s="1" t="n">
+      <c r="G58" s="1" t="n">
         <v>8434</v>
       </c>
-      <c r="G58" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H58" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J58" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D59" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="E59" s="1" t="n">
+      <c r="F59" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F59" s="1" t="n">
+      <c r="G59" s="1" t="n">
         <v>10540</v>
       </c>
-      <c r="G59" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H59" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J59" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D60" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="E60" s="1" t="n">
+      <c r="F60" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F60" s="1" t="n">
+      <c r="G60" s="1" t="n">
         <v>13763</v>
       </c>
-      <c r="G60" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H60" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J60" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D61" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="E61" s="1" t="n">
+      <c r="F61" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="F61" s="1" t="n">
+      <c r="G61" s="1" t="n">
         <v>17490</v>
       </c>
-      <c r="G61" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H61" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J61" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D62" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E62" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="F62" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="G62" s="1" t="n">
         <v>5780</v>
       </c>
-      <c r="G62" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H62" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J62" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D63" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="E63" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="F63" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F63" s="1" t="n">
+      <c r="G63" s="1" t="n">
         <v>4144</v>
       </c>
-      <c r="G63" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H63" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J63" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D64" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="E64" s="1" t="n">
+      <c r="F64" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F64" s="1" t="n">
+      <c r="G64" s="1" t="n">
         <v>4669</v>
       </c>
-      <c r="G64" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H64" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J64" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D65" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="E65" s="1" t="n">
+      <c r="F65" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F65" s="1" t="n">
+      <c r="G65" s="1" t="n">
         <v>5845</v>
       </c>
-      <c r="G65" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H65" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J65" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D66" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="E66" s="1" t="n">
+      <c r="F66" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="F66" s="1" t="n">
+      <c r="G66" s="1" t="n">
         <v>9332</v>
       </c>
-      <c r="G66" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H66" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J66" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D67" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="E67" s="1" t="n">
+      <c r="F67" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F67" s="1" t="n">
+      <c r="G67" s="1" t="n">
         <v>6767</v>
       </c>
-      <c r="G67" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H67" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J67" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D68" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E68" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="E68" s="1" t="n">
+      <c r="F68" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="F68" s="1" t="n">
+      <c r="G68" s="1" t="n">
         <v>7649</v>
       </c>
-      <c r="G68" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H68" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J68" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D69" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E69" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="E69" s="1" t="n">
+      <c r="F69" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F69" s="1" t="n">
+      <c r="G69" s="1" t="n">
         <v>8772</v>
       </c>
-      <c r="G69" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H69" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J69" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D70" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="E70" s="1" t="n">
+      <c r="F70" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="F70" s="1" t="n">
+      <c r="G70" s="1" t="n">
         <v>10121</v>
       </c>
-      <c r="G70" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H70" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J70" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D71" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E71" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="E71" s="1" t="n">
+      <c r="F71" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F71" s="1" t="n">
+      <c r="G71" s="1" t="n">
         <v>12649</v>
       </c>
-      <c r="G71" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H71" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J71" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D72" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="E72" s="1" t="n">
+      <c r="F72" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F72" s="1" t="n">
+      <c r="G72" s="1" t="n">
         <v>15140</v>
       </c>
-      <c r="G72" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H72" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J72" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D73" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="E73" s="1" t="n">
+      <c r="F73" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="F73" s="1" t="n">
+      <c r="G73" s="1" t="n">
         <v>17490</v>
       </c>
-      <c r="G73" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H73" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J73" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D74" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E74" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="F74" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="G74" s="1" t="n">
         <v>4533</v>
       </c>
-      <c r="G74" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H74" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J74" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="F75" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D75" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="E75" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="F75" s="1" t="n">
+      <c r="G75" s="1" t="n">
         <v>3051</v>
       </c>
-      <c r="G75" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H75" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J75" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D76" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="E76" s="1" t="n">
+      <c r="F76" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F76" s="1" t="n">
+      <c r="G76" s="1" t="n">
         <v>3250</v>
       </c>
-      <c r="G76" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H76" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J76" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D77" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="E77" s="1" t="n">
+      <c r="F77" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F77" s="1" t="n">
+      <c r="G77" s="1" t="n">
         <v>3450</v>
       </c>
-      <c r="G77" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H77" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J77" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D78" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="E78" s="1" t="n">
+      <c r="F78" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="F78" s="1" t="n">
+      <c r="G78" s="1" t="n">
         <v>3649</v>
       </c>
-      <c r="G78" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H78" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J78" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D79" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="E79" s="1" t="n">
+      <c r="F79" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F79" s="1" t="n">
+      <c r="G79" s="1" t="n">
         <v>3986</v>
       </c>
-      <c r="G79" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H79" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J79" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D80" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="E80" s="1" t="n">
+      <c r="F80" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="F80" s="1" t="n">
+      <c r="G80" s="1" t="n">
         <v>4265</v>
       </c>
-      <c r="G80" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H80" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J80" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D81" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="E81" s="1" t="n">
+      <c r="F81" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F81" s="1" t="n">
+      <c r="G81" s="1" t="n">
         <v>4938</v>
       </c>
-      <c r="G81" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H81" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J81" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D82" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="E82" s="1" t="n">
+      <c r="F82" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="F82" s="1" t="n">
+      <c r="G82" s="1" t="n">
         <v>6173</v>
       </c>
-      <c r="G82" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H82" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J82" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D83" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="E83" s="1" t="n">
+      <c r="F83" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F83" s="1" t="n">
+      <c r="G83" s="1" t="n">
         <v>7638</v>
       </c>
-      <c r="G83" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H83" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J83" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D84" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="E84" s="1" t="n">
+      <c r="F84" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F84" s="1" t="n">
+      <c r="G84" s="1" t="n">
         <v>9399</v>
       </c>
-      <c r="G84" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H84" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J84" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D85" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="E85" s="1" t="n">
+      <c r="F85" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="F85" s="1" t="n">
+      <c r="G85" s="1" t="n">
         <v>11230</v>
       </c>
-      <c r="G85" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H85" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J85" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D86" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E86" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E86" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="F86" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="G86" s="1" t="n">
         <v>4723</v>
       </c>
-      <c r="G86" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H86" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J86" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E87" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="F87" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D87" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="E87" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="F87" s="1" t="n">
+      <c r="G87" s="1" t="n">
         <v>3414</v>
       </c>
-      <c r="G87" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H87" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J87" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E88" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D88" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="E88" s="1" t="n">
+      <c r="F88" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F88" s="1" t="n">
+      <c r="G88" s="1" t="n">
         <v>4120</v>
       </c>
-      <c r="G88" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H88" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J88" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D89" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E89" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="E89" s="1" t="n">
+      <c r="F89" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F89" s="1" t="n">
+      <c r="G89" s="1" t="n">
         <v>4931</v>
       </c>
-      <c r="G89" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H89" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J89" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D90" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E90" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="E90" s="1" t="n">
+      <c r="F90" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="F90" s="1" t="n">
+      <c r="G90" s="1" t="n">
         <v>6905</v>
       </c>
-      <c r="G90" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H90" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J90" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D91" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E91" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="E91" s="1" t="n">
+      <c r="F91" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F91" s="1" t="n">
+      <c r="G91" s="1" t="n">
         <v>5614</v>
       </c>
-      <c r="G91" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H91" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J91" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D92" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E92" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="E92" s="1" t="n">
+      <c r="F92" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="F92" s="1" t="n">
+      <c r="G92" s="1" t="n">
         <v>6250</v>
       </c>
-      <c r="G92" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H92" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J92" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D93" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E93" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="E93" s="1" t="n">
+      <c r="F93" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F93" s="1" t="n">
+      <c r="G93" s="1" t="n">
         <v>6419</v>
       </c>
-      <c r="G93" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H93" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J93" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D94" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E94" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="E94" s="1" t="n">
+      <c r="F94" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="F94" s="1" t="n">
+      <c r="G94" s="1" t="n">
         <v>7407</v>
       </c>
-      <c r="G94" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H94" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J94" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D95" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E95" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="E95" s="1" t="n">
+      <c r="F95" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F95" s="1" t="n">
+      <c r="G95" s="1" t="n">
         <v>9165</v>
       </c>
-      <c r="G95" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H95" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J95" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D96" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E96" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="E96" s="1" t="n">
+      <c r="F96" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F96" s="1" t="n">
+      <c r="G96" s="1" t="n">
         <v>10338</v>
       </c>
-      <c r="G96" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H96" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J96" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D97" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E97" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="E97" s="1" t="n">
+      <c r="F97" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="F97" s="1" t="n">
+      <c r="G97" s="1" t="n">
         <v>11230</v>
       </c>
-      <c r="G97" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H97" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J97" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D98" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E98" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E98" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="F98" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="G98" s="1" t="n">
         <v>2406</v>
       </c>
-      <c r="G98" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H98" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J98" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D99" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E99" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="F99" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F99" s="1" t="n">
+      <c r="G99" s="1" t="n">
         <v>1825</v>
       </c>
-      <c r="G99" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H99" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J99" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D100" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E100" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="E100" s="1" t="n">
+      <c r="F100" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F100" s="1" t="n">
+      <c r="G100" s="1" t="n">
         <v>1945</v>
       </c>
-      <c r="G100" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H100" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J100" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D101" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="E101" s="1" t="n">
+      <c r="F101" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F101" s="1" t="n">
+      <c r="G101" s="1" t="n">
         <v>2064</v>
       </c>
-      <c r="G101" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H101" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J101" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D102" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="E102" s="1" t="n">
+      <c r="F102" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="F102" s="1" t="n">
+      <c r="G102" s="1" t="n">
         <v>2183</v>
       </c>
-      <c r="G102" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H102" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J102" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D103" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="E103" s="1" t="n">
+      <c r="F103" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F103" s="1" t="n">
+      <c r="G103" s="1" t="n">
         <v>2488</v>
       </c>
-      <c r="G103" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H103" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J103" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D104" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E104" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="E104" s="1" t="n">
+      <c r="F104" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="F104" s="1" t="n">
+      <c r="G104" s="1" t="n">
         <v>2662</v>
       </c>
-      <c r="G104" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H104" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J104" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D105" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="E105" s="1" t="n">
+      <c r="F105" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F105" s="1" t="n">
+      <c r="G105" s="1" t="n">
         <v>3223</v>
       </c>
-      <c r="G105" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H105" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J105" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D106" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E106" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="E106" s="1" t="n">
+      <c r="F106" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="F106" s="1" t="n">
+      <c r="G106" s="1" t="n">
         <v>4028</v>
       </c>
-      <c r="G106" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H106" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J106" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D107" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E107" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="E107" s="1" t="n">
+      <c r="F107" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F107" s="1" t="n">
+      <c r="G107" s="1" t="n">
         <v>4710</v>
       </c>
-      <c r="G107" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H107" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J107" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D108" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E108" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="E108" s="1" t="n">
+      <c r="F108" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F108" s="1" t="n">
+      <c r="G108" s="1" t="n">
         <v>5899</v>
       </c>
-      <c r="G108" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H108" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J108" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D109" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E109" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="E109" s="1" t="n">
+      <c r="F109" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="F109" s="1" t="n">
+      <c r="G109" s="1" t="n">
         <v>7139</v>
       </c>
-      <c r="G109" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H109" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J109" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D110" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E110" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E110" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="F110" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="G110" s="1" t="n">
         <v>2647</v>
       </c>
-      <c r="G110" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H110" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J110" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D111" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="E111" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="F111" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F111" s="1" t="n">
+      <c r="G111" s="1" t="n">
         <v>2138</v>
       </c>
-      <c r="G111" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H111" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J111" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D112" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E112" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="E112" s="1" t="n">
+      <c r="F112" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F112" s="1" t="n">
+      <c r="G112" s="1" t="n">
         <v>2576</v>
       </c>
-      <c r="G112" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H112" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J112" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D113" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E113" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="E113" s="1" t="n">
+      <c r="F113" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F113" s="1" t="n">
+      <c r="G113" s="1" t="n">
         <v>3352</v>
       </c>
-      <c r="G113" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H113" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J113" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D114" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E114" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="E114" s="1" t="n">
+      <c r="F114" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="F114" s="1" t="n">
+      <c r="G114" s="1" t="n">
         <v>3787</v>
       </c>
-      <c r="G114" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H114" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J114" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D115" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E115" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="E115" s="1" t="n">
+      <c r="F115" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F115" s="1" t="n">
+      <c r="G115" s="1" t="n">
         <v>3763</v>
       </c>
-      <c r="G115" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H115" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J115" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D116" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E116" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="E116" s="1" t="n">
+      <c r="F116" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="F116" s="1" t="n">
+      <c r="G116" s="1" t="n">
         <v>4012</v>
       </c>
-      <c r="G116" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H116" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J116" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D117" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E117" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="E117" s="1" t="n">
+      <c r="F117" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F117" s="1" t="n">
+      <c r="G117" s="1" t="n">
         <v>4190</v>
       </c>
-      <c r="G117" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H117" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J117" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D118" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E118" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="E118" s="1" t="n">
+      <c r="F118" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="F118" s="1" t="n">
+      <c r="G118" s="1" t="n">
         <v>4834</v>
       </c>
-      <c r="G118" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H118" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J118" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D119" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E119" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="E119" s="1" t="n">
+      <c r="F119" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F119" s="1" t="n">
+      <c r="G119" s="1" t="n">
         <v>5653</v>
       </c>
-      <c r="G119" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H119" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J119" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D120" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E120" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="E120" s="1" t="n">
+      <c r="F120" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F120" s="1" t="n">
+      <c r="G120" s="1" t="n">
         <v>6490</v>
       </c>
-      <c r="G120" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H120" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J120" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D121" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E121" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="E121" s="1" t="n">
+      <c r="F121" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="F121" s="1" t="n">
+      <c r="G121" s="1" t="n">
         <v>7139</v>
       </c>
-      <c r="G121" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H121" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J121" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
